--- a/SECTION REAL DATA ANALYSIS/Real Data Analysis.xlsx
+++ b/SECTION REAL DATA ANALYSIS/Real Data Analysis.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yifan Yang\Desktop\SUB_1 N-MATRICES\Hypothesis Testing Geisser U\SIMULATION AND REAL DATA\REAL DATA\VERSION 3.0.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yifan Yang\Desktop\SUB_1 N-MATRICES\Hypothesis Testing Geisser U\UB\UB Code VERSION 1.0.0\SECTION REAL DATA ANALYSIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B06D185-A780-4429-BA8B-29160BB1D62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4415045B-50F5-4D7F-AE3E-56A158B5949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="828" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brain Regions" sheetId="4" r:id="rId1"/>
     <sheet name="All" sheetId="7" r:id="rId2"/>
-    <sheet name="Hemisphere" sheetId="9" r:id="rId3"/>
-    <sheet name="Gender" sheetId="5" r:id="rId4"/>
-    <sheet name="Age" sheetId="8" r:id="rId5"/>
+    <sheet name="Gender" sheetId="5" r:id="rId3"/>
+    <sheet name="Age" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="493">
   <si>
     <t>pair</t>
   </si>
@@ -1513,12 +1512,6 @@
   </si>
   <si>
     <t>SFGR_Creatine</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
   </si>
   <si>
     <t>critical point</t>
@@ -1600,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1627,8 +1620,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1644,13 +1637,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4314,83 +4300,83 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E19" s="24">
+        <v>492</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="16">
         <v>310365.12920000002</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="16">
         <v>21573.856599999999</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="16">
         <v>21573.856599999999</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="16">
         <v>239953.86679999999</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="16">
         <v>22842.345799999999</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="16">
         <v>22842.345799999999</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="16">
         <v>259072.55319999999</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B20" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="16">
         <v>249.3561</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="16">
         <v>248.85980000000001</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="16">
         <v>496.09350000000001</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="16">
         <v>249.3561</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="16">
         <v>248.85980000000001</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="16">
         <v>496.09350000000001</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="16">
         <v>249.3561</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="16">
         <v>248.85980000000001</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="16">
         <v>496.09350000000001</v>
       </c>
     </row>
@@ -4398,40 +4384,40 @@
       <c r="A21" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="24">
+      <c r="B21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="16">
         <v>1</v>
       </c>
-      <c r="F21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="G21" s="24">
+      <c r="F21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G21" s="16">
         <v>1</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="16">
         <v>1</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="16">
         <v>1</v>
       </c>
-      <c r="J21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="K21" s="24">
+      <c r="J21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K21" s="16">
         <v>1</v>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="16">
         <v>1</v>
       </c>
-      <c r="M21" s="24">
+      <c r="M21" s="16">
         <v>1</v>
       </c>
     </row>
@@ -4439,40 +4425,40 @@
       <c r="A22" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E22" s="24">
-        <v>0</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="G22" s="24">
-        <v>0</v>
-      </c>
-      <c r="H22" s="24">
-        <v>0</v>
-      </c>
-      <c r="I22" s="24">
-        <v>0</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="K22" s="24">
-        <v>0</v>
-      </c>
-      <c r="L22" s="24">
-        <v>0</v>
-      </c>
-      <c r="M22" s="24">
+      <c r="B22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16">
+        <v>0</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K22" s="16">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16">
+        <v>0</v>
+      </c>
+      <c r="M22" s="16">
         <v>0</v>
       </c>
     </row>
@@ -15121,1827 +15107,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59703E-DE8E-432E-B480-B33C1F52C8C3}">
-  <dimension ref="A1:AE53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B1" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="B3" s="11">
-        <v>1.4803500000000001E-3</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11">
-        <v>1.3333850000000001E-3</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11">
-        <v>2.5743630000000001E-3</v>
-      </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11">
-        <v>2.2913780000000002E-3</v>
-      </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11">
-        <v>2.4072809999999998E-3</v>
-      </c>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11">
-        <v>2.1422899999999998E-3</v>
-      </c>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A4" s="21"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11">
-        <v>1.7055549999999999E-2</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11">
-        <v>1.6090770000000001E-2</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11">
-        <v>2.977078E-2</v>
-      </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11">
-        <v>2.8133680000000001E-2</v>
-      </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11">
-        <v>2.7232639999999999E-2</v>
-      </c>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="11">
-        <v>2.6027100000000001E-2</v>
-      </c>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="11"/>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" s="21"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11">
-        <v>3.4268640000000003E-2</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11">
-        <v>3.8277239999999997E-2</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11">
-        <v>6.0958230000000002E-2</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11">
-        <v>5.9567679999999998E-2</v>
-      </c>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11">
-        <v>5.6635060000000001E-2</v>
-      </c>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11">
-        <v>5.5515420000000003E-2</v>
-      </c>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11">
-        <v>2.7221430000000001E-2</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11">
-        <v>3.5610320000000001E-2</v>
-      </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11">
-        <v>4.9993429999999998E-2</v>
-      </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11">
-        <v>5.4718469999999998E-2</v>
-      </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11">
-        <v>4.6955070000000002E-2</v>
-      </c>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11">
-        <v>5.1219830000000001E-2</v>
-      </c>
-      <c r="AE6" s="11"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11">
-        <v>2.5221710000000001E-2</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11">
-        <v>2.804924E-2</v>
-      </c>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11">
-        <v>3.6482720000000003E-2</v>
-      </c>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11">
-        <v>3.5869770000000002E-2</v>
-      </c>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11">
-        <v>3.4500389999999999E-2</v>
-      </c>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11">
-        <v>3.3998920000000002E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>489</v>
-      </c>
-      <c r="B8" s="11">
-        <v>1.9035922E-3</v>
-      </c>
-      <c r="C8" s="11">
-        <v>3.5362810000000001E-3</v>
-      </c>
-      <c r="D8" s="11">
-        <v>-5.8895029999999997E-4</v>
-      </c>
-      <c r="E8" s="11">
-        <v>4.9443170000000002E-3</v>
-      </c>
-      <c r="F8" s="11">
-        <v>5.5059079999999995E-4</v>
-      </c>
-      <c r="G8" s="11">
-        <v>1.5151750999999999E-3</v>
-      </c>
-      <c r="H8" s="11">
-        <v>2.7274780000000002E-3</v>
-      </c>
-      <c r="I8" s="11">
-        <v>-2.876892E-4</v>
-      </c>
-      <c r="J8" s="11">
-        <v>4.0321150000000002E-3</v>
-      </c>
-      <c r="K8" s="11">
-        <v>5.69119E-5</v>
-      </c>
-      <c r="L8" s="11">
-        <v>1.5401041000000001E-3</v>
-      </c>
-      <c r="M8" s="11">
-        <v>2.3949230000000002E-3</v>
-      </c>
-      <c r="N8" s="11">
-        <v>-2.5970430000000003E-4</v>
-      </c>
-      <c r="O8" s="11">
-        <v>2.9923520000000002E-3</v>
-      </c>
-      <c r="P8" s="11">
-        <v>3.218648E-4</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>1.4421962E-3</v>
-      </c>
-      <c r="R8" s="11">
-        <v>2.2359889999999999E-3</v>
-      </c>
-      <c r="S8" s="11">
-        <v>-2.8381450000000003E-4</v>
-      </c>
-      <c r="T8" s="11">
-        <v>3.3652999999999999E-3</v>
-      </c>
-      <c r="U8" s="11">
-        <v>1.188471E-4</v>
-      </c>
-      <c r="V8" s="11">
-        <v>1.5018964999999999E-3</v>
-      </c>
-      <c r="W8" s="11">
-        <v>2.442984E-3</v>
-      </c>
-      <c r="X8" s="11">
-        <v>-1.64062E-4</v>
-      </c>
-      <c r="Y8" s="11">
-        <v>3.0665639999999999E-3</v>
-      </c>
-      <c r="Z8" s="11">
-        <v>4.0366369999999998E-4</v>
-      </c>
-      <c r="AA8" s="11">
-        <v>1.4254519E-3</v>
-      </c>
-      <c r="AB8" s="11">
-        <v>2.308961E-3</v>
-      </c>
-      <c r="AC8" s="11">
-        <v>-1.0626879999999999E-4</v>
-      </c>
-      <c r="AD8" s="11">
-        <v>3.4741580000000002E-3</v>
-      </c>
-      <c r="AE8" s="11">
-        <v>2.8287430000000001E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="11">
-        <v>3.5362810000000001E-3</v>
-      </c>
-      <c r="C9" s="11">
-        <v>1.5303891999999999E-2</v>
-      </c>
-      <c r="D9" s="11">
-        <v>2.1617855E-3</v>
-      </c>
-      <c r="E9" s="11">
-        <v>1.2466104E-2</v>
-      </c>
-      <c r="F9" s="11">
-        <v>4.1174369999999998E-3</v>
-      </c>
-      <c r="G9" s="11">
-        <v>2.7274779000000002E-3</v>
-      </c>
-      <c r="H9" s="11">
-        <v>1.4091998E-2</v>
-      </c>
-      <c r="I9" s="11">
-        <v>3.6625531999999999E-3</v>
-      </c>
-      <c r="J9" s="11">
-        <v>1.0206193000000001E-2</v>
-      </c>
-      <c r="K9" s="11">
-        <v>3.3903775000000001E-3</v>
-      </c>
-      <c r="L9" s="11">
-        <v>2.3949231999999998E-3</v>
-      </c>
-      <c r="M9" s="11">
-        <v>1.2407062999999999E-2</v>
-      </c>
-      <c r="N9" s="11">
-        <v>1.9339417E-3</v>
-      </c>
-      <c r="O9" s="11">
-        <v>6.5080069999999997E-3</v>
-      </c>
-      <c r="P9" s="11">
-        <v>2.8955366E-3</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>2.2359889999999999E-3</v>
-      </c>
-      <c r="R9" s="11">
-        <v>1.1736027E-2</v>
-      </c>
-      <c r="S9" s="11">
-        <v>2.8597785000000001E-3</v>
-      </c>
-      <c r="T9" s="11">
-        <v>6.299949E-3</v>
-      </c>
-      <c r="U9" s="11">
-        <v>3.1342631E-3</v>
-      </c>
-      <c r="V9" s="11">
-        <v>2.4429841000000001E-3</v>
-      </c>
-      <c r="W9" s="11">
-        <v>1.2393351E-2</v>
-      </c>
-      <c r="X9" s="11">
-        <v>2.1760439999999998E-3</v>
-      </c>
-      <c r="Y9" s="11">
-        <v>6.9512749999999998E-3</v>
-      </c>
-      <c r="Z9" s="11">
-        <v>3.1430284000000001E-3</v>
-      </c>
-      <c r="AA9" s="11">
-        <v>2.3089609E-3</v>
-      </c>
-      <c r="AB9" s="11">
-        <v>1.1760338E-2</v>
-      </c>
-      <c r="AC9" s="11">
-        <v>3.0593901E-3</v>
-      </c>
-      <c r="AD9" s="11">
-        <v>6.744379E-3</v>
-      </c>
-      <c r="AE9" s="11">
-        <v>3.5031684000000002E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="11">
-        <v>-5.8895029999999997E-4</v>
-      </c>
-      <c r="C10" s="11">
-        <v>2.1617860000000002E-3</v>
-      </c>
-      <c r="D10" s="11">
-        <v>3.5172768600000001E-2</v>
-      </c>
-      <c r="E10" s="11">
-        <v>-2.015448E-3</v>
-      </c>
-      <c r="F10" s="11">
-        <v>3.5051263399999998E-2</v>
-      </c>
-      <c r="G10" s="11">
-        <v>-2.876892E-4</v>
-      </c>
-      <c r="H10" s="11">
-        <v>3.6625529999999998E-3</v>
-      </c>
-      <c r="I10" s="11">
-        <v>3.9292199799999997E-2</v>
-      </c>
-      <c r="J10" s="11">
-        <v>1.5424289999999999E-3</v>
-      </c>
-      <c r="K10" s="11">
-        <v>3.75880569E-2</v>
-      </c>
-      <c r="L10" s="11">
-        <v>-2.5970430000000003E-4</v>
-      </c>
-      <c r="M10" s="11">
-        <v>1.9339419999999999E-3</v>
-      </c>
-      <c r="N10" s="11">
-        <v>2.7912104100000001E-2</v>
-      </c>
-      <c r="O10" s="11">
-        <v>-5.9731070000000001E-3</v>
-      </c>
-      <c r="P10" s="11">
-        <v>2.9567856E-2</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>-2.8381450000000003E-4</v>
-      </c>
-      <c r="R10" s="11">
-        <v>2.8597789999999998E-3</v>
-      </c>
-      <c r="S10" s="11">
-        <v>2.8372213800000001E-2</v>
-      </c>
-      <c r="T10" s="11">
-        <v>-3.8152559999999999E-3</v>
-      </c>
-      <c r="U10" s="11">
-        <v>2.89957159E-2</v>
-      </c>
-      <c r="V10" s="11">
-        <v>-1.64062E-4</v>
-      </c>
-      <c r="W10" s="11">
-        <v>2.1760439999999998E-3</v>
-      </c>
-      <c r="X10" s="11">
-        <v>2.7355216000000002E-2</v>
-      </c>
-      <c r="Y10" s="11">
-        <v>-5.1241630000000002E-3</v>
-      </c>
-      <c r="Z10" s="11">
-        <v>2.92479091E-2</v>
-      </c>
-      <c r="AA10" s="11">
-        <v>-1.0626879999999999E-4</v>
-      </c>
-      <c r="AB10" s="11">
-        <v>3.0593899999999999E-3</v>
-      </c>
-      <c r="AC10" s="11">
-        <v>2.78818274E-2</v>
-      </c>
-      <c r="AD10" s="11">
-        <v>-2.8317139999999999E-3</v>
-      </c>
-      <c r="AE10" s="11">
-        <v>2.9108690199999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="11">
-        <v>4.9443172000000002E-3</v>
-      </c>
-      <c r="C11" s="11">
-        <v>1.2466104E-2</v>
-      </c>
-      <c r="D11" s="11">
-        <v>-2.0154477999999999E-3</v>
-      </c>
-      <c r="E11" s="11">
-        <v>3.3272794000000001E-2</v>
-      </c>
-      <c r="F11" s="11">
-        <v>-1.1599229E-3</v>
-      </c>
-      <c r="G11" s="11">
-        <v>4.0321148000000001E-3</v>
-      </c>
-      <c r="H11" s="11">
-        <v>1.0206193000000001E-2</v>
-      </c>
-      <c r="I11" s="11">
-        <v>1.5424287E-3</v>
-      </c>
-      <c r="J11" s="11">
-        <v>3.1689053000000002E-2</v>
-      </c>
-      <c r="K11" s="11">
-        <v>-1.6285868000000001E-3</v>
-      </c>
-      <c r="L11" s="11">
-        <v>2.9923518000000001E-3</v>
-      </c>
-      <c r="M11" s="11">
-        <v>6.5080069999999997E-3</v>
-      </c>
-      <c r="N11" s="11">
-        <v>-5.9731068E-3</v>
-      </c>
-      <c r="O11" s="11">
-        <v>2.5079508E-2</v>
-      </c>
-      <c r="P11" s="11">
-        <v>-7.1682643999999998E-3</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>3.3652999999999999E-3</v>
-      </c>
-      <c r="R11" s="11">
-        <v>6.299949E-3</v>
-      </c>
-      <c r="S11" s="11">
-        <v>-3.8152556999999998E-3</v>
-      </c>
-      <c r="T11" s="11">
-        <v>2.8075027999999998E-2</v>
-      </c>
-      <c r="U11" s="11">
-        <v>-6.5960198000000001E-3</v>
-      </c>
-      <c r="V11" s="11">
-        <v>3.0665638999999999E-3</v>
-      </c>
-      <c r="W11" s="11">
-        <v>6.9512749999999998E-3</v>
-      </c>
-      <c r="X11" s="11">
-        <v>-5.1241630000000002E-3</v>
-      </c>
-      <c r="Y11" s="11">
-        <v>2.5022612999999999E-2</v>
-      </c>
-      <c r="Z11" s="11">
-        <v>-6.3137417999999997E-3</v>
-      </c>
-      <c r="AA11" s="11">
-        <v>3.4741576000000001E-3</v>
-      </c>
-      <c r="AB11" s="11">
-        <v>6.744379E-3</v>
-      </c>
-      <c r="AC11" s="11">
-        <v>-2.8317145000000001E-3</v>
-      </c>
-      <c r="AD11" s="11">
-        <v>2.8166678000000001E-2</v>
-      </c>
-      <c r="AE11" s="11">
-        <v>-5.5123500999999997E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="11">
-        <v>5.5059079999999995E-4</v>
-      </c>
-      <c r="C12" s="11">
-        <v>4.1174369999999998E-3</v>
-      </c>
-      <c r="D12" s="11">
-        <v>3.5051263399999998E-2</v>
-      </c>
-      <c r="E12" s="11">
-        <v>-1.159923E-3</v>
-      </c>
-      <c r="F12" s="11">
-        <v>4.4272026399999997E-2</v>
-      </c>
-      <c r="G12" s="11">
-        <v>5.69119E-5</v>
-      </c>
-      <c r="H12" s="11">
-        <v>3.3903779999999999E-3</v>
-      </c>
-      <c r="I12" s="11">
-        <v>3.75880569E-2</v>
-      </c>
-      <c r="J12" s="11">
-        <v>-1.6285869999999999E-3</v>
-      </c>
-      <c r="K12" s="11">
-        <v>4.5963376100000002E-2</v>
-      </c>
-      <c r="L12" s="11">
-        <v>3.218648E-4</v>
-      </c>
-      <c r="M12" s="11">
-        <v>2.8955370000000001E-3</v>
-      </c>
-      <c r="N12" s="11">
-        <v>2.9567856E-2</v>
-      </c>
-      <c r="O12" s="11">
-        <v>-7.1682639999999997E-3</v>
-      </c>
-      <c r="P12" s="11">
-        <v>4.1151542899999997E-2</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>1.188471E-4</v>
-      </c>
-      <c r="R12" s="11">
-        <v>3.134263E-3</v>
-      </c>
-      <c r="S12" s="11">
-        <v>2.89957159E-2</v>
-      </c>
-      <c r="T12" s="11">
-        <v>-6.5960200000000002E-3</v>
-      </c>
-      <c r="U12" s="11">
-        <v>4.3210022100000002E-2</v>
-      </c>
-      <c r="V12" s="11">
-        <v>4.0366369999999998E-4</v>
-      </c>
-      <c r="W12" s="11">
-        <v>3.143028E-3</v>
-      </c>
-      <c r="X12" s="11">
-        <v>2.9247908999999999E-2</v>
-      </c>
-      <c r="Y12" s="11">
-        <v>-6.3137419999999998E-3</v>
-      </c>
-      <c r="Z12" s="11">
-        <v>4.0460059800000003E-2</v>
-      </c>
-      <c r="AA12" s="11">
-        <v>2.8287430000000001E-4</v>
-      </c>
-      <c r="AB12" s="11">
-        <v>3.5031680000000001E-3</v>
-      </c>
-      <c r="AC12" s="11">
-        <v>2.9108690199999999E-2</v>
-      </c>
-      <c r="AD12" s="11">
-        <v>-5.5123500000000001E-3</v>
-      </c>
-      <c r="AE12" s="11">
-        <v>4.3091067500000003E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>483</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20" t="s">
-        <v>487</v>
-      </c>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="22"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="24">
-        <v>2701.6296000000002</v>
-      </c>
-      <c r="F18" s="24">
-        <v>9.8588559999999994</v>
-      </c>
-      <c r="G18" s="24">
-        <v>815.26440000000002</v>
-      </c>
-      <c r="H18" s="24">
-        <v>815.26440000000002</v>
-      </c>
-      <c r="I18" s="24">
-        <v>1680.3354999999999</v>
-      </c>
-      <c r="J18" s="24">
-        <v>9.2628789999999999</v>
-      </c>
-      <c r="K18" s="24">
-        <v>867.29510000000005</v>
-      </c>
-      <c r="L18" s="24">
-        <v>867.29510000000005</v>
-      </c>
-      <c r="M18" s="24">
-        <v>1791.8710000000001</v>
-      </c>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="22"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B19" s="24">
-        <v>16.31983</v>
-      </c>
-      <c r="C19" s="24">
-        <v>102.2728</v>
-      </c>
-      <c r="D19" s="24">
-        <v>102.3129</v>
-      </c>
-      <c r="E19" s="24">
-        <v>203.08369999999999</v>
-      </c>
-      <c r="F19" s="24">
-        <v>16.319834</v>
-      </c>
-      <c r="G19" s="24">
-        <v>102.2728</v>
-      </c>
-      <c r="H19" s="24">
-        <v>102.3129</v>
-      </c>
-      <c r="I19" s="24">
-        <v>203.08369999999999</v>
-      </c>
-      <c r="J19" s="24">
-        <v>16.319834</v>
-      </c>
-      <c r="K19" s="24">
-        <v>102.2728</v>
-      </c>
-      <c r="L19" s="24">
-        <v>102.3129</v>
-      </c>
-      <c r="M19" s="24">
-        <v>203.08369999999999</v>
-      </c>
-      <c r="O19" s="22"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="22"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="22"/>
-      <c r="Y19" s="22"/>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="22"/>
-      <c r="AC19" s="22"/>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="24">
-        <v>1</v>
-      </c>
-      <c r="F20" s="24">
-        <v>0</v>
-      </c>
-      <c r="G20" s="24">
-        <v>1</v>
-      </c>
-      <c r="H20" s="24">
-        <v>1</v>
-      </c>
-      <c r="I20" s="24">
-        <v>1</v>
-      </c>
-      <c r="J20" s="24">
-        <v>0</v>
-      </c>
-      <c r="K20" s="24">
-        <v>1</v>
-      </c>
-      <c r="L20" s="24">
-        <v>1</v>
-      </c>
-      <c r="M20" s="24">
-        <v>1</v>
-      </c>
-      <c r="O20" s="22"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="22"/>
-      <c r="Y20" s="22"/>
-      <c r="Z20" s="22"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="22"/>
-      <c r="AC20" s="22"/>
-      <c r="AD20" s="22"/>
-      <c r="AE20" s="22"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="24">
-        <v>0.52473999999999998</v>
-      </c>
-      <c r="G21" s="24">
-        <v>0</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0</v>
-      </c>
-      <c r="I21" s="24">
-        <v>0</v>
-      </c>
-      <c r="J21" s="24">
-        <v>0.59870000000000001</v>
-      </c>
-      <c r="K21" s="24">
-        <v>0</v>
-      </c>
-      <c r="L21" s="24">
-        <v>0</v>
-      </c>
-      <c r="M21" s="24">
-        <v>0</v>
-      </c>
-      <c r="O21" s="22"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="22"/>
-      <c r="Y21" s="22"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="22"/>
-      <c r="AC21" s="22"/>
-      <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="I22" s="14"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="I23" s="15"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="22"/>
-      <c r="AC24" s="22"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="22"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="I25" s="14"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="22"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="22"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="I26" s="14"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="22"/>
-      <c r="X26" s="22"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="22"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="22"/>
-      <c r="AC26" s="22"/>
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="22"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="I27" s="14"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="22"/>
-      <c r="AE27" s="22"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="I28" s="14"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="22"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="I29" s="15"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="22"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="22"/>
-      <c r="AC29" s="22"/>
-      <c r="AD29" s="22"/>
-      <c r="AE29" s="22"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="22"/>
-      <c r="AC30" s="22"/>
-      <c r="AD30" s="22"/>
-      <c r="AE30" s="22"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="22"/>
-      <c r="S31" s="22"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="22"/>
-      <c r="X31" s="22"/>
-      <c r="Y31" s="22"/>
-      <c r="Z31" s="22"/>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="22"/>
-      <c r="AC31" s="22"/>
-      <c r="AD31" s="22"/>
-      <c r="AE31" s="22"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="22"/>
-      <c r="AC32" s="22"/>
-      <c r="AD32" s="22"/>
-      <c r="AE32" s="22"/>
-    </row>
-    <row r="33" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="22"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="22"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="22"/>
-      <c r="AC33" s="22"/>
-      <c r="AD33" s="22"/>
-      <c r="AE33" s="22"/>
-    </row>
-    <row r="34" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
-      <c r="AA34" s="22"/>
-      <c r="AB34" s="22"/>
-      <c r="AC34" s="22"/>
-      <c r="AD34" s="22"/>
-      <c r="AE34" s="22"/>
-    </row>
-    <row r="35" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
-      <c r="AA35" s="22"/>
-      <c r="AB35" s="22"/>
-      <c r="AC35" s="22"/>
-      <c r="AD35" s="22"/>
-      <c r="AE35" s="22"/>
-    </row>
-    <row r="36" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
-      <c r="AA36" s="22"/>
-      <c r="AB36" s="22"/>
-      <c r="AC36" s="22"/>
-      <c r="AD36" s="22"/>
-      <c r="AE36" s="22"/>
-    </row>
-    <row r="37" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="22"/>
-      <c r="W37" s="22"/>
-      <c r="X37" s="22"/>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="22"/>
-      <c r="AA37" s="22"/>
-      <c r="AB37" s="22"/>
-      <c r="AC37" s="22"/>
-      <c r="AD37" s="22"/>
-      <c r="AE37" s="22"/>
-    </row>
-    <row r="38" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
-      <c r="AA38" s="22"/>
-      <c r="AB38" s="22"/>
-      <c r="AC38" s="22"/>
-      <c r="AD38" s="22"/>
-      <c r="AE38" s="22"/>
-    </row>
-    <row r="39" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-    </row>
-    <row r="40" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O40" s="22"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="22"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="22"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="22"/>
-      <c r="AC40" s="22"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-    </row>
-    <row r="41" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O41" s="22"/>
-      <c r="P41" s="22"/>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="22"/>
-      <c r="S41" s="22"/>
-      <c r="T41" s="22"/>
-      <c r="U41" s="22"/>
-      <c r="V41" s="22"/>
-      <c r="W41" s="22"/>
-      <c r="X41" s="22"/>
-      <c r="Y41" s="22"/>
-      <c r="Z41" s="22"/>
-      <c r="AA41" s="22"/>
-      <c r="AB41" s="22"/>
-      <c r="AC41" s="22"/>
-      <c r="AD41" s="22"/>
-      <c r="AE41" s="22"/>
-    </row>
-    <row r="42" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="22"/>
-      <c r="S42" s="22"/>
-      <c r="T42" s="22"/>
-      <c r="U42" s="22"/>
-      <c r="V42" s="22"/>
-      <c r="W42" s="22"/>
-      <c r="X42" s="22"/>
-      <c r="Y42" s="22"/>
-      <c r="Z42" s="22"/>
-      <c r="AA42" s="22"/>
-      <c r="AB42" s="22"/>
-      <c r="AC42" s="22"/>
-      <c r="AD42" s="22"/>
-      <c r="AE42" s="22"/>
-    </row>
-    <row r="43" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O43" s="22"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="22"/>
-      <c r="S43" s="22"/>
-      <c r="T43" s="22"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="22"/>
-      <c r="W43" s="22"/>
-      <c r="X43" s="22"/>
-      <c r="Y43" s="22"/>
-      <c r="Z43" s="22"/>
-      <c r="AA43" s="22"/>
-      <c r="AB43" s="22"/>
-      <c r="AC43" s="22"/>
-      <c r="AD43" s="22"/>
-      <c r="AE43" s="22"/>
-    </row>
-    <row r="44" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O44" s="22"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="22"/>
-      <c r="S44" s="22"/>
-      <c r="T44" s="22"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="22"/>
-      <c r="W44" s="22"/>
-      <c r="X44" s="22"/>
-      <c r="Y44" s="22"/>
-      <c r="Z44" s="22"/>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="22"/>
-      <c r="AC44" s="22"/>
-      <c r="AD44" s="22"/>
-      <c r="AE44" s="22"/>
-    </row>
-    <row r="45" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O45" s="22"/>
-      <c r="P45" s="22"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
-      <c r="W45" s="22"/>
-      <c r="X45" s="22"/>
-      <c r="Y45" s="22"/>
-      <c r="Z45" s="22"/>
-      <c r="AA45" s="22"/>
-      <c r="AB45" s="22"/>
-      <c r="AC45" s="22"/>
-      <c r="AD45" s="22"/>
-      <c r="AE45" s="22"/>
-    </row>
-    <row r="46" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="22"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="22"/>
-      <c r="AC46" s="22"/>
-      <c r="AD46" s="22"/>
-      <c r="AE46" s="22"/>
-    </row>
-    <row r="47" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O47" s="22"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="22"/>
-      <c r="R47" s="22"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="22"/>
-      <c r="U47" s="22"/>
-      <c r="V47" s="22"/>
-      <c r="W47" s="22"/>
-      <c r="X47" s="22"/>
-      <c r="Y47" s="22"/>
-      <c r="Z47" s="22"/>
-      <c r="AA47" s="22"/>
-      <c r="AB47" s="22"/>
-      <c r="AC47" s="22"/>
-      <c r="AD47" s="22"/>
-      <c r="AE47" s="22"/>
-    </row>
-    <row r="48" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O48" s="22"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="22"/>
-      <c r="R48" s="22"/>
-      <c r="S48" s="22"/>
-      <c r="T48" s="22"/>
-      <c r="U48" s="22"/>
-      <c r="V48" s="22"/>
-      <c r="W48" s="22"/>
-      <c r="X48" s="22"/>
-      <c r="Y48" s="22"/>
-      <c r="Z48" s="22"/>
-      <c r="AA48" s="22"/>
-      <c r="AB48" s="22"/>
-      <c r="AC48" s="22"/>
-      <c r="AD48" s="22"/>
-      <c r="AE48" s="22"/>
-    </row>
-    <row r="49" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="22"/>
-      <c r="S49" s="22"/>
-      <c r="T49" s="22"/>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
-      <c r="Y49" s="22"/>
-      <c r="Z49" s="22"/>
-      <c r="AA49" s="22"/>
-      <c r="AB49" s="22"/>
-      <c r="AC49" s="22"/>
-      <c r="AD49" s="22"/>
-      <c r="AE49" s="22"/>
-    </row>
-    <row r="50" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
-      <c r="S50" s="22"/>
-      <c r="T50" s="22"/>
-      <c r="U50" s="22"/>
-      <c r="V50" s="22"/>
-      <c r="W50" s="22"/>
-      <c r="X50" s="22"/>
-      <c r="Y50" s="22"/>
-      <c r="Z50" s="22"/>
-      <c r="AA50" s="22"/>
-      <c r="AB50" s="22"/>
-      <c r="AC50" s="22"/>
-      <c r="AD50" s="22"/>
-      <c r="AE50" s="22"/>
-    </row>
-    <row r="51" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O51" s="22"/>
-      <c r="P51" s="22"/>
-      <c r="Q51" s="22"/>
-      <c r="R51" s="22"/>
-      <c r="S51" s="22"/>
-      <c r="T51" s="22"/>
-      <c r="U51" s="22"/>
-      <c r="V51" s="22"/>
-      <c r="W51" s="22"/>
-      <c r="X51" s="22"/>
-      <c r="Y51" s="22"/>
-      <c r="Z51" s="22"/>
-      <c r="AA51" s="22"/>
-      <c r="AB51" s="22"/>
-      <c r="AC51" s="22"/>
-      <c r="AD51" s="22"/>
-      <c r="AE51" s="22"/>
-    </row>
-    <row r="52" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O52" s="22"/>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
-      <c r="R52" s="22"/>
-      <c r="S52" s="22"/>
-      <c r="T52" s="22"/>
-      <c r="U52" s="22"/>
-      <c r="V52" s="22"/>
-      <c r="W52" s="22"/>
-      <c r="X52" s="22"/>
-      <c r="Y52" s="22"/>
-      <c r="Z52" s="22"/>
-      <c r="AA52" s="22"/>
-      <c r="AB52" s="22"/>
-      <c r="AC52" s="22"/>
-      <c r="AD52" s="22"/>
-      <c r="AE52" s="22"/>
-    </row>
-    <row r="53" spans="15:31" x14ac:dyDescent="0.3">
-      <c r="O53" s="22"/>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
-      <c r="R53" s="22"/>
-      <c r="S53" s="22"/>
-      <c r="T53" s="22"/>
-      <c r="U53" s="22"/>
-      <c r="V53" s="22"/>
-      <c r="W53" s="22"/>
-      <c r="X53" s="22"/>
-      <c r="Y53" s="22"/>
-      <c r="Z53" s="22"/>
-      <c r="AA53" s="22"/>
-      <c r="AB53" s="22"/>
-      <c r="AC53" s="22"/>
-      <c r="AD53" s="22"/>
-      <c r="AE53" s="22"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="V1:AE1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="AA2:AE2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CDB0AE2-9BED-47F6-B9CA-5DFFAB974DDD}">
   <dimension ref="A1:AE21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -17809,83 +15974,83 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="24">
+        <v>492</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="16">
         <v>1711.9013</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="16">
         <v>28.111750000000001</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="16">
         <v>510.2176</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="16">
         <v>510.2176</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="16">
         <v>1011.3286000000001</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="16">
         <v>35.533769999999997</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="16">
         <v>567.14639999999997</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="16">
         <v>567.14639999999997</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="16">
         <v>1126.0975000000001</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B19" s="24">
+        <v>491</v>
+      </c>
+      <c r="B19" s="16">
         <v>17.073229999999999</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="16">
         <v>252.54859999999999</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="16">
         <v>252.62299999999999</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="16">
         <v>496.27339999999998</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="16">
         <v>17.073229999999999</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="16">
         <v>252.54859999999999</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="16">
         <v>252.62299999999999</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="16">
         <v>496.27339999999998</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="16">
         <v>17.073229999999999</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="16">
         <v>252.54859999999999</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="16">
         <v>252.62299999999999</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="16">
         <v>496.27339999999998</v>
       </c>
     </row>
@@ -17893,40 +16058,40 @@
       <c r="A20" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="24">
+      <c r="B20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="16">
         <v>1</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="16">
         <v>1</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="16">
         <v>1</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="16">
         <v>1</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="16">
         <v>1</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="16">
         <v>1</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="16">
         <v>1</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="16">
         <v>1</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="16">
         <v>1</v>
       </c>
     </row>
@@ -17934,40 +16099,40 @@
       <c r="A21" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="24">
-        <v>0</v>
-      </c>
-      <c r="G21" s="24">
-        <v>0</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0</v>
-      </c>
-      <c r="I21" s="24">
-        <v>0</v>
-      </c>
-      <c r="J21" s="24">
-        <v>0</v>
-      </c>
-      <c r="K21" s="24">
-        <v>0</v>
-      </c>
-      <c r="L21" s="24">
-        <v>0</v>
-      </c>
-      <c r="M21" s="24">
+      <c r="B21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0</v>
+      </c>
+      <c r="J21" s="16">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
         <v>0</v>
       </c>
     </row>
@@ -17993,7 +16158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F961838-AD77-442A-B0B9-26EDA4020BE1}">
   <dimension ref="A1:AT21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -19227,83 +17392,83 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="24">
+        <v>492</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="16">
         <v>5036.7394000000004</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="16">
         <v>180.59594000000001</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="16">
         <v>1471.5716</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="16">
         <v>1471.5716</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="16">
         <v>3053.1448999999998</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="16">
         <v>184.17102</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="16">
         <v>1641.3474000000001</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="16">
         <v>1641.3474000000001</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="16">
         <v>3417.2952</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B19" s="24">
+        <v>491</v>
+      </c>
+      <c r="B19" s="16">
         <v>31.45204</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="16">
         <v>493.35860000000002</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="16">
         <v>493.37029999999999</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="16">
         <v>962.99170000000004</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="16">
         <v>31.45204</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="16">
         <v>493.35860000000002</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="16">
         <v>493.37029999999999</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="16">
         <v>962.99170000000004</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="16">
         <v>31.45204</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="16">
         <v>493.35860000000002</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="16">
         <v>493.37029999999999</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="16">
         <v>962.99170000000004</v>
       </c>
     </row>
@@ -19311,40 +17476,40 @@
       <c r="A20" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="24">
+      <c r="B20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="16">
         <v>1</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="16">
         <v>1</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="16">
         <v>1</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="16">
         <v>1</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="16">
         <v>1</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="16">
         <v>1</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="16">
         <v>1</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="16">
         <v>1</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="16">
         <v>1</v>
       </c>
     </row>
@@ -19352,45 +17517,54 @@
       <c r="A21" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="24">
-        <v>0</v>
-      </c>
-      <c r="G21" s="24">
-        <v>0</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0</v>
-      </c>
-      <c r="I21" s="24">
-        <v>0</v>
-      </c>
-      <c r="J21" s="24">
-        <v>0</v>
-      </c>
-      <c r="K21" s="24">
-        <v>0</v>
-      </c>
-      <c r="L21" s="24">
-        <v>0</v>
-      </c>
-      <c r="M21" s="24">
+      <c r="B21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0</v>
+      </c>
+      <c r="J21" s="16">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Q1:AE1"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:Z2"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="AF1:AT1"/>
     <mergeCell ref="AF2:AJ2"/>
     <mergeCell ref="AK2:AO2"/>
@@ -19400,15 +17574,6 @@
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="L2:P2"/>
     <mergeCell ref="B1:P1"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="Q1:AE1"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="AA2:AE2"/>
-    <mergeCell ref="A8:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
